--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-07-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£11.00</t>
+          <t>£12.44</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£15.55</t>
+          <t>£16.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4060-2400x1200x60mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4090-2400x1200x90mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£41.48</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£51.88</t>
+          <t>£43.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£42.48</t>
+          <t>£48.00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£181.56</t>
+          <t>£63.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£18.08</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£18.08</t>
+          <t>£480.00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£25.48</t>
+          <t>£38.82</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£10.08</t>
+          <t>£28.98</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
